--- a/data/trans_orig/IP1003-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89338</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96169</t>
+          <t>96159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182736</t>
+          <t>182785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193722</t>
+          <t>193889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>75499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>83778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74828</t>
+          <t>75654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82951</t>
+          <t>83400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155133</t>
+          <t>154951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165265</t>
+          <t>165574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59185</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>66028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84650</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94236</t>
+          <t>94447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146471</t>
+          <t>146860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158147</t>
+          <t>158899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186791</t>
+          <t>186987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196088</t>
+          <t>196208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182618</t>
+          <t>182973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193945</t>
+          <t>194067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>373727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388398</t>
+          <t>388385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90985</t>
+          <t>90970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99630</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116765</t>
+          <t>116487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124297</t>
+          <t>124626</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>211256</t>
+          <t>209889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222991</t>
+          <t>222954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73511</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59656</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68294</t>
+          <t>68322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129443</t>
+          <t>129476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139875</t>
+          <t>140024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35479</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>69665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99727</t>
+          <t>98791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589987</t>
+          <t>588581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609029</t>
+          <t>608613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627822</t>
+          <t>627524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>649124</t>
+          <t>648250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1223732</t>
+          <t>1224668</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1252653</t>
+          <t>1253794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78982</t>
+          <t>79460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86565</t>
+          <t>86636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84214</t>
+          <t>84168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89142</t>
+          <t>89146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165893</t>
+          <t>166647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174961</t>
+          <t>175417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85347</t>
+          <t>85038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>91398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88240</t>
+          <t>88125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>94633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176140</t>
+          <t>176513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184852</t>
+          <t>184829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83494</t>
+          <t>83420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82271</t>
+          <t>81724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>161710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169567</t>
+          <t>169055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192587</t>
+          <t>192894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202180</t>
+          <t>202187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>194209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209724</t>
+          <t>209493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390809</t>
+          <t>391262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409050</t>
+          <t>409356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28060</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129432</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141522</t>
+          <t>141815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135886</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260943</t>
+          <t>260149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275179</t>
+          <t>274827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>65535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119091</t>
+          <t>119212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126517</t>
+          <t>126494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53684</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>60181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88177</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631620</t>
+          <t>633171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>651626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659817</t>
+          <t>660079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681361</t>
+          <t>681094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1298778</t>
+          <t>1299121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1326844</t>
+          <t>1326774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>71923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80100</t>
+          <t>80269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>93170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167906</t>
+          <t>167565</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177988</t>
+          <t>178160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99011</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>105065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101782</t>
+          <t>102041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110060</t>
+          <t>110393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203948</t>
+          <t>204426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213432</t>
+          <t>213667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>73536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126040</t>
+          <t>126672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134451</t>
+          <t>134581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>30692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206089</t>
+          <t>206073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217161</t>
+          <t>216716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194179</t>
+          <t>194400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205043</t>
+          <t>205229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>405078</t>
+          <t>403739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419956</t>
+          <t>419380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20431</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123141</t>
+          <t>123573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132485</t>
+          <t>132532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131302</t>
+          <t>131008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140212</t>
+          <t>140391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258851</t>
+          <t>256797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271411</t>
+          <t>270881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>54758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60472</t>
+          <t>60464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57555</t>
+          <t>57107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65678</t>
+          <t>65713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115530</t>
+          <t>115899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125022</t>
+          <t>125500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52722</t>
+          <t>53434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>79263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630717</t>
+          <t>629372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648083</t>
+          <t>648978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>666450</t>
+          <t>665913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>684180</t>
+          <t>685149</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1302319</t>
+          <t>1301976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1328517</t>
+          <t>1327805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92971</t>
+          <t>93050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100850</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117508</t>
+          <t>118247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130881</t>
+          <t>130590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214333</t>
+          <t>214283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229032</t>
+          <t>229418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>84963</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92576</t>
+          <t>92720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80986</t>
+          <t>81408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91783</t>
+          <t>92098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170216</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183328</t>
+          <t>183258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43709</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50362</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>51952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61883</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>99162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110875</t>
+          <t>110698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>22941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>40399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>195497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209690</t>
+          <t>209490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193087</t>
+          <t>194328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208988</t>
+          <t>208756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396458</t>
+          <t>394880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415754</t>
+          <t>414997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108595</t>
+          <t>108679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116518</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134162</t>
+          <t>133620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150343</t>
+          <t>150421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245670</t>
+          <t>246412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264432</t>
+          <t>264616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>62788</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68237</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69616</t>
+          <t>69536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127079</t>
+          <t>127493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136602</t>
+          <t>136779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>47642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>49397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>79869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81694</t>
+          <t>81496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118814</t>
+          <t>117534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607999</t>
+          <t>608239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>629192</t>
+          <t>628810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>666749</t>
+          <t>667562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>697110</t>
+          <t>698034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1284498</t>
+          <t>1285778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321618</t>
+          <t>1321816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
